--- a/TestData/data1.xlsx
+++ b/TestData/data1.xlsx
@@ -8,22 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f535686d8cbe6146/Desktop/Playwright_tutorial/TestData/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_75D2FFBBB1F7204EE3CAC412D1AC6C428B1F48BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1198B1BA-8CF8-4523-9A20-FA6275A01B9A}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="11_75D2FFBBB1F7204EE3CAC412D1AC6C428B1F48BA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C88662FB-5DD8-4638-B3AA-BA4C88CA68F9}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10416" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="768" yWindow="768" windowWidth="17280" windowHeight="10416" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="sample" sheetId="1" r:id="rId1"/>
     <sheet name="Login" sheetId="2" r:id="rId2"/>
     <sheet name="ParaBank_Login" sheetId="3" r:id="rId3"/>
     <sheet name="OpenAcc" sheetId="4" r:id="rId4"/>
+    <sheet name="BookingDetails" sheetId="5" r:id="rId5"/>
+    <sheet name="Amazon" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="21">
   <si>
     <t>Account Type</t>
   </si>
@@ -65,6 +67,27 @@
   </si>
   <si>
     <t>13677</t>
+  </si>
+  <si>
+    <t>source</t>
+  </si>
+  <si>
+    <t>destination</t>
+  </si>
+  <si>
+    <t>Departure</t>
+  </si>
+  <si>
+    <t>Bengaluru</t>
+  </si>
+  <si>
+    <t>Kolkata</t>
+  </si>
+  <si>
+    <t>phone name</t>
+  </si>
+  <si>
+    <t>iphone 16</t>
   </si>
 </sst>
 </file>
@@ -142,6 +165,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -560,4 +587,53 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E4901913-CF43-4620-94F6-FC4F1DB4CA19}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2618B2C0-B00B-4FAD-AD7E-3D893CE50851}">
+  <dimension ref="A1:A2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>